--- a/input/Template_EMIS_Access_PTR.xlsx
+++ b/input/Template_EMIS_Access_PTR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acted-my.sharepoint.com/personal/martina_vit_impact-initiatives_org/Documents/PiN_app_dev/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="443" documentId="8_{D63770E9-8D5C-4F2A-BD7D-98D3C6683B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB93B9E7-FCAA-4092-9779-2202E5EB6006}"/>
+  <xr:revisionPtr revIDLastSave="444" documentId="8_{D63770E9-8D5C-4F2A-BD7D-98D3C6683B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F51B9730-FDA8-466F-A0B1-75C68C54C3A1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{24D09A16-471A-4A7F-BD10-C475AB78837D}"/>
+    <workbookView xWindow="28635" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{24D09A16-471A-4A7F-BD10-C475AB78837D}"/>
   </bookViews>
   <sheets>
     <sheet name="indicator" sheetId="3" r:id="rId1"/>
@@ -65,7 +65,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{2DEB68FB-5E7F-4B6B-8D64-71751F1A5F63}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{CB5E418C-5F06-40B9-97A8-6F84E0046CA1}">
       <text>
         <r>
           <rPr>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Admin Pcode</t>
   </si>
@@ -120,10 +120,34 @@
     <t>Secondary school -- Enrolled students</t>
   </si>
   <si>
-    <t>Number of teachers</t>
-  </si>
-  <si>
     <t>threshold PTR (Change it according to the context average PTR)</t>
+  </si>
+  <si>
+    <t>school PTR</t>
+  </si>
+  <si>
+    <t>sev4 - Protection indicator value -- continuous / discrete numerical variable</t>
+  </si>
+  <si>
+    <t>sev4 - threshold for numerical variable --&gt; if above the child is in need</t>
+  </si>
+  <si>
+    <t>sev4 - Protection indicator value -- categorical variable</t>
+  </si>
+  <si>
+    <t>sev4 - category for categorical variable --&gt; if selected the child is in need</t>
+  </si>
+  <si>
+    <t>sev5 - Protection indicator value -- continuous / discrete numerical variable</t>
+  </si>
+  <si>
+    <t>sev5 - threshold for numerical variable --&gt; if above the child is in need</t>
+  </si>
+  <si>
+    <t>sev5 - Protection indicator value -- categorical variable</t>
+  </si>
+  <si>
+    <t>sev5 - category for categorical variable --&gt; if selected the child is in need</t>
   </si>
 </sst>
 </file>
@@ -179,7 +203,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -190,6 +214,19 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
       </patternFill>
+    </fill>
+    <fill>
+      <gradientFill degree="135">
+        <stop position="0">
+          <color theme="0"/>
+        </stop>
+        <stop position="0.5">
+          <color rgb="FFFFFFCC"/>
+        </stop>
+        <stop position="1">
+          <color theme="0"/>
+        </stop>
+      </gradientFill>
     </fill>
   </fills>
   <borders count="2">
@@ -221,13 +258,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -239,6 +273,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -580,26 +618,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17DEB9B6-621B-4484-8A08-69293BE9C3A3}">
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R1"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="2" width="14.140625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" style="6" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" customWidth="1"/>
-    <col min="6" max="6" width="21.7109375" style="6" customWidth="1"/>
-    <col min="7" max="7" width="37" style="6" customWidth="1"/>
-    <col min="8" max="10" width="22.85546875" style="3" customWidth="1"/>
+    <col min="1" max="2" width="14.1328125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="21.7265625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="11.86328125" customWidth="1"/>
+    <col min="5" max="5" width="10.26953125" customWidth="1"/>
+    <col min="6" max="6" width="21.7265625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="37" style="5" customWidth="1"/>
+    <col min="8" max="8" width="21.86328125" style="7" customWidth="1"/>
+    <col min="9" max="9" width="22.54296875" style="7" customWidth="1"/>
+    <col min="10" max="10" width="23.54296875" style="7" customWidth="1"/>
+    <col min="11" max="11" width="25.1328125" style="7" customWidth="1"/>
+    <col min="12" max="12" width="21.86328125" style="7" customWidth="1"/>
+    <col min="13" max="13" width="22.54296875" style="7" customWidth="1"/>
+    <col min="14" max="14" width="23.54296875" style="7" customWidth="1"/>
+    <col min="15" max="15" width="25.1328125" style="7" customWidth="1"/>
+    <col min="16" max="18" width="22.86328125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:18" ht="59" x14ac:dyDescent="0.75">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -608,24 +654,45 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
     </row>
   </sheetData>
   <protectedRanges>

--- a/input/Template_EMIS_Access_PTR.xlsx
+++ b/input/Template_EMIS_Access_PTR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acted-my.sharepoint.com/personal/martina_vit_impact-initiatives_org/Documents/PiN_app_dev/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="444" documentId="8_{D63770E9-8D5C-4F2A-BD7D-98D3C6683B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F51B9730-FDA8-466F-A0B1-75C68C54C3A1}"/>
+  <xr:revisionPtr revIDLastSave="446" documentId="8_{D63770E9-8D5C-4F2A-BD7D-98D3C6683B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18F35B92-A378-4E96-8E7A-C6E57E7BCB1C}"/>
   <bookViews>
-    <workbookView xWindow="28635" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{24D09A16-471A-4A7F-BD10-C475AB78837D}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{24D09A16-471A-4A7F-BD10-C475AB78837D}"/>
   </bookViews>
   <sheets>
     <sheet name="indicator" sheetId="3" r:id="rId1"/>
@@ -65,7 +65,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{CB5E418C-5F06-40B9-97A8-6F84E0046CA1}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{CB5E418C-5F06-40B9-97A8-6F84E0046CA1}">
       <text>
         <r>
           <rPr>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Admin Pcode</t>
   </si>
@@ -105,49 +105,10 @@
     <t>Enrolled students -- Children/Enfants (5-17)</t>
   </si>
   <si>
-    <t>Enrolled Girls/Filles (5-17)</t>
-  </si>
-  <si>
-    <t>Enrolled Boys/Garcons (5-17)</t>
-  </si>
-  <si>
-    <t>Primary school -- Enrolled students</t>
-  </si>
-  <si>
-    <t>Intermediate school or secondary school  -- Enrolled students</t>
-  </si>
-  <si>
-    <t>Secondary school -- Enrolled students</t>
-  </si>
-  <si>
     <t>threshold PTR (Change it according to the context average PTR)</t>
   </si>
   <si>
     <t>school PTR</t>
-  </si>
-  <si>
-    <t>sev4 - Protection indicator value -- continuous / discrete numerical variable</t>
-  </si>
-  <si>
-    <t>sev4 - threshold for numerical variable --&gt; if above the child is in need</t>
-  </si>
-  <si>
-    <t>sev4 - Protection indicator value -- categorical variable</t>
-  </si>
-  <si>
-    <t>sev4 - category for categorical variable --&gt; if selected the child is in need</t>
-  </si>
-  <si>
-    <t>sev5 - Protection indicator value -- continuous / discrete numerical variable</t>
-  </si>
-  <si>
-    <t>sev5 - threshold for numerical variable --&gt; if above the child is in need</t>
-  </si>
-  <si>
-    <t>sev5 - Protection indicator value -- categorical variable</t>
-  </si>
-  <si>
-    <t>sev5 - category for categorical variable --&gt; if selected the child is in need</t>
   </si>
 </sst>
 </file>
@@ -203,7 +164,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -214,19 +175,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
       </patternFill>
-    </fill>
-    <fill>
-      <gradientFill degree="135">
-        <stop position="0">
-          <color theme="0"/>
-        </stop>
-        <stop position="0.5">
-          <color rgb="FFFFFFCC"/>
-        </stop>
-        <stop position="1">
-          <color theme="0"/>
-        </stop>
-      </gradientFill>
     </fill>
   </fills>
   <borders count="2">
@@ -258,14 +206,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -273,10 +215,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -618,80 +556,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17DEB9B6-621B-4484-8A08-69293BE9C3A3}">
-  <dimension ref="A1:R1"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="14.1328125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="21.7265625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="11.86328125" customWidth="1"/>
-    <col min="5" max="5" width="10.26953125" customWidth="1"/>
-    <col min="6" max="6" width="21.7265625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="37" style="5" customWidth="1"/>
-    <col min="8" max="8" width="21.86328125" style="7" customWidth="1"/>
-    <col min="9" max="9" width="22.54296875" style="7" customWidth="1"/>
-    <col min="10" max="10" width="23.54296875" style="7" customWidth="1"/>
-    <col min="11" max="11" width="25.1328125" style="7" customWidth="1"/>
-    <col min="12" max="12" width="21.86328125" style="7" customWidth="1"/>
-    <col min="13" max="13" width="22.54296875" style="7" customWidth="1"/>
-    <col min="14" max="14" width="23.54296875" style="7" customWidth="1"/>
-    <col min="15" max="15" width="25.1328125" style="7" customWidth="1"/>
-    <col min="16" max="18" width="22.86328125" style="2" customWidth="1"/>
+    <col min="1" max="2" width="14.140625" style="3" customWidth="1"/>
+    <col min="3" max="4" width="21.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="37" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="59" x14ac:dyDescent="0.75">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
